--- a/artfynd/A 25314-2026 artfynd.xlsx
+++ b/artfynd/A 25314-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054947</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136054948</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136054949</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 25314-2026 artfynd.xlsx
+++ b/artfynd/A 25314-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136054947</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136054948</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136054949</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
